--- a/dashboard/data/Book A Librarian Export Q3 AY22-23 - Deidentified.xlsx
+++ b/dashboard/data/Book A Librarian Export Q3 AY22-23 - Deidentified.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="67">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -163,7 +163,7 @@
     <t xml:space="preserve">ELEC 704 Bioethics </t>
   </si>
   <si>
-    <t xml:space="preserve"> Tell us your idea in 2 sentences or keep it a secret.  Your choice!: I would like to discuss library resources for use in the ELEC 704 Bioethics Course.}</t>
+    <t xml:space="preserve">Not Coded</t>
   </si>
   <si>
     <t xml:space="preserve">  Tell us about your research project in 3 sentences.: I am focusing on maxillomandubular advancement surgery for patients with obstructive sleep apnea. I would like to further refine it to a comparison with other treatments, but I’m afraid that has been done before. My other option is to focus on timing of the surgery, as in the what the patient has to try first. </t>
@@ -187,9 +187,6 @@
     <t xml:space="preserve">Virtual </t>
   </si>
   <si>
-    <t xml:space="preserve"> Tell us about your research project in 3 sentences.: Looking for resources and a topic for my bioethics paper. }</t>
-  </si>
-  <si>
     <t xml:space="preserve">Event Type: Group</t>
   </si>
   <si>
@@ -200,15 +197,6 @@
   </si>
   <si>
     <t xml:space="preserve">  Tell us about your research project in 3 sentences.: The purpose of this project is to determine clear, measure, and evidence-based graduation criteria as well as a formalized remediation process for the Indigo APP Urgent Care Fellowship.}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tell us about your research project in 3 sentences.: I am hoping to do my paper on how we as doctors should manage strong beliefs that impact our interactions with patients/patient care. I worked with an FM resident who is a very strict catholic. Due to her religious beliefs, she has chosen not to provide any kind of birth control care to her patients and only offers the family planning method. She says she counsels patients on all their options but will have them schedule an appointment with a different doctor if they want an IUD, or nexplanon, or some other birth control form. I feel that this is an ethically ambiguous way to practice and would like to explore this further. }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tell us about your research project in 3 sentences.: I will write a paper on the ethics of vaccine refusal. I will discuss the moral and ethical obligations of getting vaccines vs autonomy and the right to do what you want with your own body. I will analyze these topics in various cultural, societal, and ethical contexts.  }</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tell us about your research project in 3 sentences.: I will write a paper on the ethics of vaccine refusal. I will write about individual autonomy of doing what we want vs the ethics of protecting others. I will analyzw this in various societal and cutlural contexts. }</t>
   </si>
   <si>
     <t xml:space="preserve"> Tell us if you need access to specific resource.: I just have questions about how to appropriately send out NPTE practice questions to the class via email while properly citing the sources. I also heard that there may be an updated NPTE Prep book added to our library soon and would like more info on that</t>
@@ -590,8 +578,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="26.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="98.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="26.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16382" style="0" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1457,11 +1444,11 @@
       <c r="G30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1487,7 +1474,7 @@
         <v>17</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>14</v>
@@ -1510,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>14</v>
@@ -1544,11 +1531,11 @@
       <c r="G33" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>56</v>
+      <c r="H33" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1573,11 +1560,11 @@
       <c r="G34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>57</v>
+      <c r="H34" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1602,11 +1589,11 @@
       <c r="G35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>58</v>
+      <c r="H35" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1632,7 +1619,7 @@
         <v>12</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>14</v>
@@ -1661,7 +1648,7 @@
         <v>17</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>14</v>
@@ -1690,7 +1677,7 @@
         <v>17</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>14</v>
@@ -1719,7 +1706,7 @@
         <v>17</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>14</v>
@@ -1748,7 +1735,7 @@
         <v>17</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>14</v>
@@ -1777,7 +1764,7 @@
         <v>21</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>14</v>
@@ -1788,7 +1775,7 @@
         <v>45009</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>10</v>
@@ -1800,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1829,10 +1816,10 @@
         <v>16</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1858,7 +1845,7 @@
         <v>17</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>14</v>
@@ -1887,7 +1874,7 @@
         <v>12</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>14</v>
